--- a/extenbooks/ES1201.xlsx
+++ b/extenbooks/ES1201.xlsx
@@ -1081,11 +1081,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_assembly</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1201 — NSW/GDP (ST 2002) — PENDING</t>
+          <t># ES1201 — NSW/GDP (Shaikh &amp; Tonak 2002)</t>
         </is>
       </c>
     </row>
@@ -1257,87 +1257,91 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Chapter**: External study — ST 2002. **Status**: validated_book_and_extension.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NSW (S607-COMBINED 1952-2025) divided by GDP (BEA NIPA 1.7.5 Line 1). 74 years. 1952=-2.59%, 1997=-1.11%, 2024=+4.21% (positive). Range [-3.68%, +8.48%]. Confirms ST 2002's headline — NSW shifts from negative (workers subsidizing state) toward positive (net transfers to workers) over the postwar era.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>needs GDP</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>`data/raw/bea/nipa_1_7_5_gross_output_by_industry.csv` Line 1 (cached). S607-COMBINED from extended Ch6 work.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>S607 / GDP (BEA NIPA Table 1.1.5)</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. "The Welfare State and the Myth of the Social Wage" revisited. (ST 2002 paper / Cherry et al. book chapter).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1201.xlsx
+++ b/extenbooks/ES1201.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 3</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–1997</t>
+          <t>1952-2025</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1234,112 +1234,149 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1201-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shaikh &amp; Tonak 2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1201 — NSW/GDP (Shaikh &amp; Tonak 2002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: External study — ST 2002. **Status**: validated_book_and_extension.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1201 — NSW/GDP (Shaikh &amp; Tonak 2002)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NSW (S607-COMBINED 1952-2025) divided by GDP (BEA NIPA 1.7.5 Line 1). 74 years. 1952=-2.59%, 1997=-1.11%, 2024=+4.21% (positive). Range [-3.68%, +8.48%]. Confirms ST 2002's headline — NSW shifts from negative (workers subsidizing state) toward positive (net transfers to workers) over the postwar era.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>**Chapter**: External study — ST 2002. **Status**: validated_book_and_extension.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>`data/raw/bea/nipa_1_7_5_gross_output_by_industry.csv` Line 1 (cached). S607-COMBINED from extended Ch6 work.</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NSW (S607-COMBINED 1952-2025) divided by GDP (BEA NIPA 1.7.5 Line 1). 74 years. 1952=-2.59%, 1997=-1.11%, 2024=+4.21% (positive). Range [-3.68%, +8.48%]. Confirms ST 2002's headline — NSW shifts from negative (workers subsidizing state) toward positive (net transfers to workers) over the postwar era.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>## Citation</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. "The Welfare State and the Myth of the Social Wage" revisited. (ST 2002 paper / Cherry et al. book chapter).</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>`data/raw/bea/nipa_1_7_5_gross_output_by_industry.csv` Line 1 (cached). S607-COMBINED from extended Ch6 work.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. "The Welfare State and the Myth of the Social Wage" revisited. (ST 2002 paper / Cherry et al. book chapter).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1356,10 +1393,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1384,235 +1421,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NSW/GDP is the net social wage expressed as a fraction of nominal GDP. The net social wage is computed as NSW = NSW1 + NSW2 = (E1 - T1) + (E2 - T2)*LS, where E1 = direct labor benefits (income support, housing, labor training); E2 = social consumption expenditures (education, health, transport, recreation) allocated by labor share LS; T1 = total Social Security taxes; T2 = personal income taxes, property taxes, motor vehicle licenses, and other personal taxes. LS = wages and salaries / total personal income. Denominator GDP normalizes the NSW to the size of the economy.</t>
+          <t>VERBATIM (Moos 2017, p.3 Abstract): "In this paper, I examine the trends of fiscal transfers between the state and workers during 1959 - 2012 to understand the net impact of redistributive policy in the United States. This paper presents original net social wage data from and analysis based on the replication and extension of Shaikh and Tonak (2002). The paper investigates the appearance of a post-2001 variation in the net social wage data. The positive net social wage in the 21st century is the result of a combination of factors including the growth of income support, healthcare inflation, neoliberal tax reforms, and macroeconomic instability." Defines Moos's NSW/GDP replication-and-extension scope that ES1201 operationalizes.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_2002, pp.248-250; full_transcription.md FORMULAS AND DEFINITIONS section</t>
+          <t>EXTERNAL: Moos, Katherine A. 2017. 'Neoliberal Redistributive Policy: The U.S. Net Social Wage in the 21st Century.' UMass Amherst Working Paper 2017-18, Abstract, p.3. Verbatim from Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2017_Moos_NSW_21st_Century/full_transcription.md (Abstract section).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Over the full postwar period 1952-1997, the net social wage as a percentage of GDP is very modest. The NSW/EC ratio averages 0.6% of employee compensation — effectively zero. NSW/GDP is within narrow bounds of +/-3% for most of the period (Shaikh 2003 notes the NSW was within +/-3% of GDP). This confirms that workers' taxes largely pay for their own social benefits with no net redistribution from capital.</t>
+          <t>VERBATIM (Moos 2017, Section 3, transcription line 118): "The NSW series presented in this paper differs slightly from Shaikh and Tonak's series. This may be due, at least in part, because the NIPA tables were revised several times since Shaikh and Tonak's data was constructed, including a comprehensive revision in 1999. ... The differences in the series in the overlap years (1959 - 1997) are slight (approximately 1 percent of GDP). For this reason, the variation in the series is assumed to be the result of revisions of NIPA data and the series used in this paper can be considered a faithful reconstruction of Shaikh and Tonak's series." Authoritative external statement of the NIPA-revision divergence that ES1201 inherits.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_2002, p.253 Fig 29.3; p.255 Summary and Conclusions; full_transcription.md KEY FINDING section</t>
+          <t>EXTERNAL: Moos 2017, Section 3 'Extended Net Social Wage Data Series', pp.4-5. Verbatim from Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2017_Moos_NSW_21st_Century/full_transcription.md line 118.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>phase_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Three historical phases are identified. Phase 1 (1952-1969 Boom): NSW ratio negative (net labor tax), ranging -2% to -7% of EC. Phase 2 (1969-1975 Crisis onset): NSW rises sharply into positive territory, peaking around +9% of EC (~+5% of GDP) in 1975, driven by rising unemployment and automatic stabilizers. Phase 3 (Reagan-Bush attack, 1975-1989): Counterattack by capital and state drives NSW back to negative despite high unemployment. Phase 4 (Clinton era, 1989-1997): NSW returns to near zero; noncyclical benefit base raised modestly but tax ratio converges; by 1997 NSW essentially zero.</t>
+          <t>VERBATIM (Moos 2017, Section 4, transcription line 150): "In Figure 1, we see that the net social wage/GDP ratio has been positive since the 1970s. Even more strikingly, after 2002, the net social wage / GDP ratio is at a very high level for a decade. In 2010, it reaches a high of 8.6 percent of GDP." This is the headline 21st-century divergence that ES1201's extension to 2012 must reproduce; benchmark for V11 (max NSW/GDP = 0.086 in 2010).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_2002, pp.251-254; full_transcription.md ANALYSIS OF TRENDS and HISTORICAL PHASES SUMMARY sections</t>
+          <t>EXTERNAL: Moos 2017, Section 4 'The Net Social Wage in the 21st Century', p.6. Verbatim from Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2017_Moos_NSW_21st_Century/full_transcription.md line 150.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Primary data source: BEA National Income and Product Accounts (NIPA), Survey of Current Business. Annual data 1952-1997 (45 years). All figures in billions of current dollars. Real wages expressed in 1982 constant dollars using CPI. Labor share computed as wages and salaries / total personal income. Full year-by-year data provided in paper Appendix (pp.258-265).</t>
+          <t>when considering the impact on worker incomes, it is more appropriate to look at the net social wage: social benefit expenditures received by workers minus taxes paid by them.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_2002, pp.258-265 Appendix; full_transcription.md DATA SOURCES AND METHODOLOGY section</t>
+          <t>Shaikh &amp; Tonak 2002, Introduction, p.248</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ES1201 = NSW / GDP, where NSW = E1 - T1 + (E2 - T2)*LS. Components from NIPA: E1 = income support + housing + labor training; E2 = education + health/hospitals + recreation + energy + natural resources + passenger transportation + postal; T1 = employee + employer Social Security contributions; T2 = federal + state/local income taxes + motor vehicle licenses + personal property taxes + other personal taxes/nontaxes.</t>
+          <t>over the postwar period from 1952 to 1997, the net social wage as a percentage of employee compensation is very modest indeed: It seldom fluctuates beyond ±4 percent ... Its average is a mere 0.6 percent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ST_2002, Table 29.1 p.250; full_transcription.md TABLE 29.1 and SUMMARY OF KEY FORMULAS sections</t>
+          <t>Shaikh &amp; Tonak 2002, Principal Findings, p.248</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>benchmark_value</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1964 benchmark (Table 29.1): E1=34.08bn, E2=50.02bn, T1=30.08bn, T2=60.43bn, LS=0.708, EC=209.37bn. NSW1=(34.08-30.08)=+4.01bn, NSW2=(50.02-60.43)*0.708=-7.50bn, Total NSW=-3.49bn. NSW/EC = -3.49/209.37 = -1.67%. Labor share stable over period: ranges 0.69-0.73, with values 0.711 (1952), 0.708 (1964), 0.721 (1980), 0.691 (1997).</t>
+          <t>In effect, social wage flows largely recirculate income among wage and salary earners as a whole.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ST_2002, Table 29.1 p.250; Appendix tables pp.258-265; full_transcription.md APPENDIX TABLE section</t>
+          <t>Shaikh &amp; Tonak 2002, Implication, p.248</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cyclical_driver</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Year-to-year movements strongly affected by unemployment rate. When unemployment rises: (1) government spending on welfare, unemployment insurance rises; (2) tax revenues fall as employment shrinks and workers drop to lower brackets. Both effects raise NSW. Same mechanism connects NSW to budget deficits — both are endogenous responses to unemployment, not causally related to each other. This is demonstrated in Figure 29.5 (NSW and deficit/EC).</t>
+          <t>NSW/GDP is the net social wage expressed as a fraction of nominal GDP. The net social wage is computed as NSW = NSW1 + NSW2 = (E1 - T1) + (E2 - T2)*LS, where E1 = direct labor benefits (income support, housing, labor training); E2 = social consumption expenditures (education, health, transport, recreation) allocated by labor share LS; T1 = total Social Security taxes; T2 = personal income taxes, property taxes, motor vehicle licenses, and other personal taxes. LS = wages and salaries / total personal income. Denominator GDP normalizes the NSW to the size of the economy.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ST_2002, pp.254-256; full_transcription.md UNEMPLOYMENT AND NET SOCIAL WAGE section</t>
+          <t>ST_2002, pp.248-250; full_transcription.md FORMULAS AND DEFINITIONS section</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodological_note</t>
+          <t>key_finding</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Study uses observed incidence (actual taxes paid) not hypothetical tax-shifting incidence. Excludes from labor benefits: military retirement/disability, transfer payments to businesses, general administration, defense, and faux frais. Excludes from labor taxes: corporate profit taxes, indirect business taxes, estate and gift taxes. E2 expenditures allocated to labor via labor share LS because they benefit both labor and capital.</t>
+          <t>Over the full postwar period 1952-1997, the net social wage as a percentage of GDP is very modest. The NSW/EC ratio averages 0.6% of employee compensation — effectively zero. NSW/GDP is within narrow bounds of +/-3% for most of the period (Shaikh 2003 notes the NSW was within +/-3% of GDP). This confirms that workers' taxes largely pay for their own social benefits with no net redistribution from capital.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ST_2002, pp.248-249, Notes 1-3 pp.256-257; full_transcription.md MEASURING THE SOCIAL WAGE and METHODOLOGICAL CONTRIBUTIONS sections</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>ST_2002, p.253 Fig 29.3; p.255 Summary and Conclusions; full_transcription.md KEY FINDING section</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>phase_description</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Three historical phases are identified. Phase 1 (1952-1969 Boom): NSW ratio negative (net labor tax), ranging -2% to -7% of EC. Phase 2 (1969-1975 Crisis onset): NSW rises sharply into positive territory, peaking around +9% of EC (~+5% of GDP) in 1975, driven by rising unemployment and automatic stabilizers. Phase 3 (Reagan-Bush attack, 1975-1989): Counterattack by capital and state drives NSW back to negative despite high unemployment. Phase 4 (Clinton era, 1989-1997): NSW returns to near zero; noncyclical benefit base raised modestly but tax ratio converges; by 1997 NSW essentially zero.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_2002, pp.251-254; full_transcription.md ANALYSIS OF TRENDS and HISTORICAL PHASES SUMMARY sections</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NSW/GDP ratio from Shaikh &amp; Tonak (2002), covering the full postwar period 1952-1997. Derived as (E1-T1+(E2-T2)*LS)/GDP using NIPA data. Average value essentially zero over the 45-year period; fluctuates within +/-3% of GDP driven primarily by unemployment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Primary data source: BEA National Income and Product Accounts (NIPA), Survey of Current Business. Annual data 1952-1997 (45 years). All figures in billions of current dollars. Real wages expressed in 1982 constant dollars using CPI. Labor share computed as wages and salaries / total personal income. Full year-by-year data provided in paper Appendix (pp.258-265).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_2002, pp.258-265 Appendix; full_transcription.md DATA SOURCES AND METHODOLOGY section</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ES1201 = NSW / GDP, where NSW = E1 - T1 + (E2 - T2)*LS. Components from NIPA: E1 = income support + housing + labor training; E2 = education + health/hospitals + recreation + energy + natural resources + passenger transportation + postal; T1 = employee + employer Social Security contributions; T2 = federal + state/local income taxes + motor vehicle licenses + personal property taxes + other personal taxes/nontaxes.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_2002, Table 29.1 p.250; full_transcription.md TABLE 29.1 and SUMMARY OF KEY FORMULAS sections</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>benchmark_value</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1964 benchmark (Table 29.1): E1=34.08bn, E2=50.02bn, T1=30.08bn, T2=60.43bn, LS=0.708, EC=209.37bn. NSW1=(34.08-30.08)=+4.01bn, NSW2=(50.02-60.43)*0.708=-7.50bn, Total NSW=-3.49bn. NSW/EC = -3.49/209.37 = -1.67%. Labor share stable over period: ranges 0.69-0.73, with values 0.711 (1952), 0.708 (1964), 0.721 (1980), 0.691 (1997).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ST_2002, Table 29.1 p.250; Appendix tables pp.258-265; full_transcription.md APPENDIX TABLE section</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cyclical_driver</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NIPA tables revised since paper was published (1999 comprehensive revision); Moos (2017) replication shows ~1 percentage point difference attributable to NIPA revisions</t>
+          <t>Year-to-year movements strongly affected by unemployment rate. When unemployment rises: (1) government spending on welfare, unemployment insurance rises; (2) tax revenues fall as employment shrinks and workers drop to lower brackets. Both effects raise NSW. Same mechanism connects NSW to budget deficits — both are endogenous responses to unemployment, not causally related to each other. This is demonstrated in Figure 29.5 (NSW and deficit/EC).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST_2002, pp.254-256; full_transcription.md UNEMPLOYMENT AND NET SOCIAL WAGE section</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>methodological_note</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Labor share measure uses wages+salaries/total personal income; does not exclude corporate officers or include self-employed wage equivalent (authors note these offset each other)</t>
+          <t>Study uses observed incidence (actual taxes paid) not hypothetical tax-shifting incidence. Excludes from labor benefits: military retirement/disability, transfer payments to businesses, general administration, defense, and faux frais. Excludes from labor taxes: corporate profit taxes, indirect business taxes, estate and gift taxes. E2 expenditures allocated to labor via labor share LS because they benefit both labor and capital.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ST_2002, pp.248-249, Notes 1-3 pp.256-257; full_transcription.md MEASURING THE SOCIAL WAGE and METHODOLOGICAL CONTRIBUTIONS sections</t>
         </is>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES1202</t>
-        </is>
-      </c>
+          <t>when considering the impact on worker incomes, it is more appropriate to look at the net social wage: social benefit expenditures received by workers minus taxes paid by them.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S607</t>
-        </is>
-      </c>
+          <t>over the postwar period from 1952 to 1997, the net social wage as a percentage of employee compensation is very modest indeed: It seldom fluctuates beyond ±4 percent ... Its average is a mere 0.6 percent</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ES1301</t>
-        </is>
-      </c>
+          <t>In effect, social wage flows largely recirculate income among wage and salary earners as a whole.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ST_2002</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. 'The Rise and Fall of the U.S. Welfare State.' In Political Economy and Contemporary Capitalism, ed. Boushey, Baiman, and Saunders. M.E. Sharpe, Armonk. pp. 247-265.</t>
-        </is>
-      </c>
-    </row>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NSW/GDP ratio from Shaikh &amp; Tonak (2002), covering the full postwar period 1952-1997. Derived as (E1-T1+(E2-T2)*LS)/GDP using NIPA data. Average value essentially zero over the 45-year period; fluctuates within +/-3% of GDP driven primarily by unemployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NIPA tables revised since paper was published (1999 comprehensive revision); Moos (2017) replication shows ~1 percentage point difference attributable to NIPA revisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Labor share measure uses wages+salaries/total personal income; does not exclude corporate officers or include self-employed wage equivalent (authors note these offset each other)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ES1202</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S607</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ES1301</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ST_2002</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. 'The Rise and Fall of the U.S. Welfare State.' In Political Economy and Contemporary Capitalism, ed. Boushey, Baiman, and Saunders. M.E. Sharpe, Armonk. pp. 247-265.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. Survey of Current Business, various years.</t>
         </is>
@@ -1629,7 +1805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1700,7 +1876,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1897,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1964": -0.0167, "1997": 0.006, "2010": 0.086}</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1921,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
